--- a/Result/profitability/8415.xlsx
+++ b/Result/profitability/8415.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM59"/>
+  <dimension ref="A1:AM60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.04</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6562499999999999</v>
+        <v>0.6925</v>
       </c>
       <c r="N2" t="n">
-        <v>37.3275</v>
+        <v>38.16375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.17</v>
       </c>
       <c r="M3" t="n">
-        <v>0.57125</v>
+        <v>0.67875</v>
       </c>
       <c r="N3" t="n">
-        <v>37.69875</v>
+        <v>38.62</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.01</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5375</v>
+        <v>0.5874999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>37.79499999999999</v>
+        <v>38.60125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.03</v>
       </c>
       <c r="M5" t="n">
-        <v>0.44875</v>
+        <v>0.53125</v>
       </c>
       <c r="N5" t="n">
-        <v>37.845</v>
+        <v>38.02875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -7923,6 +7923,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>8415</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>7458</v>
+      </c>
+      <c r="D60" t="n">
+        <v>4480</v>
+      </c>
+      <c r="E60" t="n">
+        <v>2978</v>
+      </c>
+      <c r="F60" t="n">
+        <v>39.93</v>
+      </c>
+      <c r="G60" t="n">
+        <v>1694</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>22.71%</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>-37</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1656</v>
+      </c>
+      <c r="K60" t="n">
+        <v>1169</v>
+      </c>
+      <c r="L60" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0.79375</v>
+      </c>
+      <c r="N60" t="n">
+        <v>36.54125</v>
+      </c>
+      <c r="O60" t="n">
+        <v>1</v>
+      </c>
+      <c r="P60" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>1</v>
+      </c>
+      <c r="R60" t="n">
+        <v>1</v>
+      </c>
+      <c r="S60" t="n">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
+      </c>
+      <c r="V60" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W60" t="n">
+        <v>0.1099999999999999</v>
+      </c>
+      <c r="X60" t="n">
+        <v>0.1067961165048543</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>0.8599999999999994</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>0.02201177373944208</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>0.6599999999999999</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>1.469999999999999</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>0.03822152886115449</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF60" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG60" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH60" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI60" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK60" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL60" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM60" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
